--- a/DOH_Spec_Checks.xlsx
+++ b/DOH_Spec_Checks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DOH\eadoh_public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78951CF-DB97-4CF9-A472-F30EC1A2DA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124A6FD3-5B9D-45BA-B31A-4FAB38E6DD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
